--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Aircraft_Cumulative_Statistics_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Aircraft_Cumulative_Statistics_2025.xlsx
@@ -13,78 +13,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Breeze</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-500</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A220-100</t>
+  </si>
+  <si>
+    <t>A220-300</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A320NEO</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B737-9</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A330-900</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B787-10</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -166,10 +205,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -189,40 +228,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -230,40 +269,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>52407147994</v>
+        <v>3120944830</v>
       </c>
       <c r="C2" s="0">
-        <v>63165337815</v>
+        <v>3695825554</v>
       </c>
       <c r="D2" s="0">
-        <v>723046</v>
+        <v>79276</v>
       </c>
       <c r="E2" s="0">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>264452</v>
+        <v>233231</v>
       </c>
       <c r="G2" s="0">
-        <v>3.0299999999999998</v>
+        <v>5</v>
       </c>
       <c r="H2" s="0">
-        <v>10.640000000000001</v>
+        <v>7.3799999999999999</v>
       </c>
       <c r="I2" s="0">
-        <v>82.969999999999999</v>
+        <v>84.450000000000003</v>
       </c>
       <c r="J2" s="0">
-        <v>1390</v>
+        <v>317</v>
       </c>
       <c r="K2" s="0">
-        <v>4809</v>
+        <v>1830.75</v>
       </c>
       <c r="L2" s="0">
-        <v>28.039999999999999</v>
+        <v>36.619999999999997</v>
       </c>
       <c r="M2" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.17000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -271,40 +310,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>15636297157</v>
+        <v>1562581593</v>
       </c>
       <c r="C3" s="0">
-        <v>18940038942</v>
+        <v>2109008000</v>
       </c>
       <c r="D3" s="0">
-        <v>415808</v>
+        <v>44806</v>
       </c>
       <c r="E3" s="0">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>119342</v>
+        <v>128998</v>
       </c>
       <c r="G3" s="0">
-        <v>2.6200000000000001</v>
+        <v>2.7400000000000002</v>
       </c>
       <c r="H3" s="0">
-        <v>6.3700000000000001</v>
+        <v>4.0899999999999999</v>
       </c>
       <c r="I3" s="0">
-        <v>82.560000000000002</v>
+        <v>74.090000000000003</v>
       </c>
       <c r="J3" s="0">
-        <v>910</v>
+        <v>327</v>
       </c>
       <c r="K3" s="0">
-        <v>5460</v>
+        <v>2069.23</v>
       </c>
       <c r="L3" s="0">
-        <v>31.32</v>
+        <v>41.380000000000003</v>
       </c>
       <c r="M3" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="4">
@@ -312,40 +351,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>222364981546</v>
+        <v>2200181667</v>
       </c>
       <c r="C4" s="0">
-        <v>264765133935</v>
+        <v>2709362587</v>
       </c>
       <c r="D4" s="0">
-        <v>730891</v>
+        <v>44365</v>
       </c>
       <c r="E4" s="0">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="F4" s="0">
-        <v>1175237</v>
+        <v>100184</v>
       </c>
       <c r="G4" s="0">
-        <v>3.2400000000000002</v>
+        <v>1.6399999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>9.9499999999999993</v>
+        <v>2.7000000000000002</v>
       </c>
       <c r="I4" s="0">
-        <v>83.989999999999995</v>
+        <v>81.209999999999994</v>
       </c>
       <c r="J4" s="0">
-        <v>1184</v>
+        <v>411</v>
       </c>
       <c r="K4" s="0">
-        <v>7008</v>
+        <v>1787.53</v>
       </c>
       <c r="L4" s="0">
-        <v>37.780000000000001</v>
+        <v>27.149999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="5">
@@ -353,40 +392,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>5484574707</v>
+        <v>39244051208</v>
       </c>
       <c r="C5" s="0">
-        <v>7129604553</v>
+        <v>48807922861</v>
       </c>
       <c r="D5" s="0">
-        <v>400090</v>
+        <v>142359</v>
       </c>
       <c r="E5" s="0">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="F5" s="0">
-        <v>61579</v>
+        <v>1242759</v>
       </c>
       <c r="G5" s="0">
-        <v>3.46</v>
+        <v>3.6200000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>8.4800000000000004</v>
+        <v>6.71</v>
       </c>
       <c r="I5" s="0">
-        <v>76.930000000000007</v>
+        <v>80.409999999999997</v>
       </c>
       <c r="J5" s="0">
-        <v>857</v>
+        <v>524</v>
       </c>
       <c r="K5" s="0">
-        <v>4259</v>
+        <v>1538.8199999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>31.530000000000001</v>
+        <v>20.559999999999999</v>
       </c>
       <c r="M5" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="6">
@@ -394,40 +433,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>233986395369</v>
+        <v>1731201783</v>
       </c>
       <c r="C6" s="0">
-        <v>278381772629</v>
+        <v>2151823450</v>
       </c>
       <c r="D6" s="0">
-        <v>787012</v>
+        <v>63345</v>
       </c>
       <c r="E6" s="0">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F6" s="0">
-        <v>1172551</v>
+        <v>123689</v>
       </c>
       <c r="G6" s="0">
-        <v>3.3100000000000001</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>10.210000000000001</v>
+        <v>5.6399999999999997</v>
       </c>
       <c r="I6" s="0">
-        <v>84.049999999999997</v>
+        <v>80.450000000000003</v>
       </c>
       <c r="J6" s="0">
-        <v>1212</v>
+        <v>348</v>
       </c>
       <c r="K6" s="0">
-        <v>6382</v>
+        <v>2097.0900000000001</v>
       </c>
       <c r="L6" s="0">
-        <v>33.659999999999997</v>
+        <v>41.939999999999998</v>
       </c>
       <c r="M6" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +474,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>31153012118</v>
+        <v>6422303636</v>
       </c>
       <c r="C7" s="0">
-        <v>39706835428</v>
+        <v>8124646224</v>
       </c>
       <c r="D7" s="0">
-        <v>667005</v>
+        <v>98936</v>
       </c>
       <c r="E7" s="0">
-        <v>209</v>
+        <v>66</v>
       </c>
       <c r="F7" s="0">
-        <v>205620</v>
+        <v>278194</v>
       </c>
       <c r="G7" s="0">
-        <v>3.4500000000000002</v>
+        <v>3.3900000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>9.0899999999999999</v>
+        <v>5.7400000000000002</v>
       </c>
       <c r="I7" s="0">
-        <v>78.459999999999994</v>
+        <v>79.049999999999997</v>
       </c>
       <c r="J7" s="0">
-        <v>918</v>
+        <v>444</v>
       </c>
       <c r="K7" s="0">
-        <v>5002</v>
+        <v>2337.5799999999999</v>
       </c>
       <c r="L7" s="0">
-        <v>23.82</v>
+        <v>35.560000000000002</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.13600000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +515,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>19301382543</v>
+        <v>715214100</v>
       </c>
       <c r="C8" s="0">
-        <v>23203025381</v>
+        <v>915843610</v>
       </c>
       <c r="D8" s="0">
-        <v>950554</v>
+        <v>131966</v>
       </c>
       <c r="E8" s="0">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="F8" s="0">
-        <v>84085</v>
+        <v>18623</v>
       </c>
       <c r="G8" s="0">
-        <v>3.4399999999999999</v>
+        <v>2.6800000000000002</v>
       </c>
       <c r="H8" s="0">
-        <v>9.5999999999999996</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="I8" s="0">
-        <v>83.180000000000007</v>
+        <v>78.090000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>1159</v>
+        <v>477</v>
       </c>
       <c r="K8" s="0">
-        <v>7973</v>
+        <v>7281.5299999999997</v>
       </c>
       <c r="L8" s="0">
-        <v>35.25</v>
+        <v>71</v>
       </c>
       <c r="M8" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +556,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>53559619102</v>
+        <v>12064589320</v>
       </c>
       <c r="C9" s="0">
-        <v>65021176247</v>
+        <v>15021992569</v>
       </c>
       <c r="D9" s="0">
-        <v>618190</v>
+        <v>136464</v>
       </c>
       <c r="E9" s="0">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="F9" s="0">
-        <v>310105</v>
+        <v>439981</v>
       </c>
       <c r="G9" s="0">
-        <v>2.9500000000000002</v>
+        <v>4</v>
       </c>
       <c r="H9" s="0">
-        <v>9.8599999999999994</v>
+        <v>6.8200000000000003</v>
       </c>
       <c r="I9" s="0">
-        <v>82.370000000000005</v>
+        <v>80.310000000000002</v>
       </c>
       <c r="J9" s="0">
-        <v>1297</v>
+        <v>454</v>
       </c>
       <c r="K9" s="0">
-        <v>5577</v>
+        <v>2159.73</v>
       </c>
       <c r="L9" s="0">
-        <v>34.700000000000003</v>
+        <v>28.699999999999999</v>
       </c>
       <c r="M9" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +597,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>139458641208</v>
+        <v>4196143473</v>
       </c>
       <c r="C10" s="0">
-        <v>180064926062</v>
+        <v>5111581351</v>
       </c>
       <c r="D10" s="0">
-        <v>613175</v>
+        <v>315530</v>
       </c>
       <c r="E10" s="0">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="F10" s="0">
-        <v>1415926</v>
+        <v>50553</v>
       </c>
       <c r="G10" s="0">
-        <v>4.8200000000000003</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>10.300000000000001</v>
+        <v>8.2599999999999998</v>
       </c>
       <c r="I10" s="0">
-        <v>77.450000000000003</v>
+        <v>82.090000000000003</v>
       </c>
       <c r="J10" s="0">
-        <v>780</v>
+        <v>928</v>
       </c>
       <c r="K10" s="0">
-        <v>4761</v>
+        <v>4985.6499999999996</v>
       </c>
       <c r="L10" s="0">
-        <v>29.300000000000001</v>
+        <v>45.75</v>
       </c>
       <c r="M10" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +638,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>31323133561</v>
+        <v>15882915527</v>
       </c>
       <c r="C11" s="0">
-        <v>39944295863</v>
+        <v>19809443626</v>
       </c>
       <c r="D11" s="0">
-        <v>547782</v>
+        <v>447772</v>
       </c>
       <c r="E11" s="0">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="F11" s="0">
-        <v>215836</v>
+        <v>158596</v>
       </c>
       <c r="G11" s="0">
-        <v>2.96</v>
+        <v>3.5800000000000001</v>
       </c>
       <c r="H11" s="0">
-        <v>7.6699999999999999</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="I11" s="0">
-        <v>78.420000000000002</v>
+        <v>80.180000000000007</v>
       </c>
       <c r="J11" s="0">
-        <v>957</v>
+        <v>919</v>
       </c>
       <c r="K11" s="0">
-        <v>5113</v>
+        <v>5050.1999999999998</v>
       </c>
       <c r="L11" s="0">
-        <v>26.460000000000001</v>
+        <v>37.109999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +679,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>6052836622</v>
+        <v>31319540146</v>
       </c>
       <c r="C12" s="0">
-        <v>7799993854</v>
+        <v>38454560061</v>
       </c>
       <c r="D12" s="0">
-        <v>352462</v>
+        <v>351633</v>
       </c>
       <c r="E12" s="0">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="F12" s="0">
-        <v>37398</v>
+        <v>402609</v>
       </c>
       <c r="G12" s="0">
-        <v>1.6899999999999999</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="H12" s="0">
-        <v>5.04</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="I12" s="0">
-        <v>77.599999999999994</v>
+        <v>81.450000000000003</v>
       </c>
       <c r="J12" s="0">
-        <v>1130</v>
+        <v>730</v>
       </c>
       <c r="K12" s="0">
-        <v>5626</v>
+        <v>4956.46</v>
       </c>
       <c r="L12" s="0">
-        <v>30.460000000000001</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="M12" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +720,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>254371378828</v>
+        <v>66911351659</v>
       </c>
       <c r="C13" s="0">
-        <v>309449760908</v>
+        <v>82401204498</v>
       </c>
       <c r="D13" s="0">
-        <v>835402</v>
+        <v>494813</v>
       </c>
       <c r="E13" s="0">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F13" s="0">
-        <v>1013537</v>
+        <v>547446</v>
       </c>
       <c r="G13" s="0">
-        <v>2.7400000000000002</v>
+        <v>3.29</v>
       </c>
       <c r="H13" s="0">
-        <v>10.18</v>
+        <v>8.3699999999999992</v>
       </c>
       <c r="I13" s="0">
-        <v>82.200000000000003</v>
+        <v>81.200000000000003</v>
       </c>
       <c r="J13" s="0">
-        <v>1510</v>
+        <v>922</v>
       </c>
       <c r="K13" s="0">
-        <v>6739</v>
+        <v>5611.25</v>
       </c>
       <c r="L13" s="0">
-        <v>34.460000000000001</v>
+        <v>34.439999999999998</v>
       </c>
       <c r="M13" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +761,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1333844725</v>
+        <v>23750015633</v>
       </c>
       <c r="C14" s="0">
-        <v>1583426825</v>
+        <v>29514200404</v>
       </c>
       <c r="D14" s="0">
-        <v>73579</v>
+        <v>536134</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="F14" s="0">
-        <v>84613</v>
+        <v>176467</v>
       </c>
       <c r="G14" s="0">
-        <v>3.9300000000000002</v>
+        <v>3.21</v>
       </c>
       <c r="H14" s="0">
-        <v>6.04</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="I14" s="0">
-        <v>84.239999999999995</v>
+        <v>80.469999999999999</v>
       </c>
       <c r="J14" s="0">
-        <v>373</v>
+        <v>921</v>
       </c>
       <c r="K14" s="0">
-        <v>1648</v>
+        <v>4666.3699999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>32.880000000000003</v>
+        <v>25.66</v>
       </c>
       <c r="M14" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +802,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>6678329212</v>
+        <v>101016757403</v>
       </c>
       <c r="C15" s="0">
-        <v>8382640866</v>
+        <v>120700316516</v>
       </c>
       <c r="D15" s="0">
-        <v>185088</v>
+        <v>729969</v>
       </c>
       <c r="E15" s="0">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="F15" s="0">
-        <v>250544</v>
+        <v>557701</v>
       </c>
       <c r="G15" s="0">
-        <v>5.5300000000000002</v>
+        <v>3.3700000000000001</v>
       </c>
       <c r="H15" s="0">
-        <v>9.3800000000000008</v>
+        <v>10.289999999999999</v>
       </c>
       <c r="I15" s="0">
-        <v>79.670000000000002</v>
+        <v>83.689999999999998</v>
       </c>
       <c r="J15" s="0">
-        <v>449</v>
+        <v>1165</v>
       </c>
       <c r="K15" s="0">
-        <v>1724</v>
+        <v>5951.0900000000001</v>
       </c>
       <c r="L15" s="0">
-        <v>23.140000000000001</v>
+        <v>31.84</v>
       </c>
       <c r="M15" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +843,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>10187243794</v>
+        <v>90493835556</v>
       </c>
       <c r="C16" s="0">
-        <v>12416284803</v>
+        <v>109179795315</v>
       </c>
       <c r="D16" s="0">
-        <v>66490</v>
+        <v>857052</v>
       </c>
       <c r="E16" s="0">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="F16" s="0">
-        <v>322932</v>
+        <v>356273</v>
       </c>
       <c r="G16" s="0">
-        <v>1.73</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="H16" s="0">
-        <v>3.1200000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="I16" s="0">
-        <v>82.049999999999997</v>
+        <v>82.890000000000001</v>
       </c>
       <c r="J16" s="0">
-        <v>521</v>
+        <v>1534</v>
       </c>
       <c r="K16" s="0">
-        <v>1950</v>
+        <v>5816</v>
       </c>
       <c r="L16" s="0">
-        <v>26.57</v>
+        <v>28.91</v>
       </c>
       <c r="M16" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.071999999999999995</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +884,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1186997580</v>
+        <v>6111034075</v>
       </c>
       <c r="C17" s="0">
-        <v>1410434550</v>
+        <v>7392077785</v>
       </c>
       <c r="D17" s="0">
-        <v>66940</v>
+        <v>206829</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="F17" s="0">
-        <v>75533</v>
+        <v>190920</v>
       </c>
       <c r="G17" s="0">
-        <v>3.5800000000000001</v>
+        <v>5.3399999999999999</v>
       </c>
       <c r="H17" s="0">
-        <v>5.9000000000000004</v>
+        <v>6.8399999999999999</v>
       </c>
       <c r="I17" s="0">
-        <v>84.159999999999997</v>
+        <v>82.670000000000002</v>
       </c>
       <c r="J17" s="0">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="K17" s="0">
-        <v>2146</v>
+        <v>5128.9300000000003</v>
       </c>
       <c r="L17" s="0">
-        <v>42.920000000000002</v>
+        <v>45.399999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.19</v>
+        <v>0.17000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +925,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>2957441017</v>
+        <v>51233067668</v>
       </c>
       <c r="C18" s="0">
-        <v>3583820052</v>
+        <v>65999534459</v>
       </c>
       <c r="D18" s="0">
-        <v>214857</v>
+        <v>468447</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="F18" s="0">
-        <v>101988</v>
+        <v>676781</v>
       </c>
       <c r="G18" s="0">
-        <v>6.1100000000000003</v>
+        <v>4.7999999999999998</v>
       </c>
       <c r="H18" s="0">
-        <v>9.6400000000000006</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="I18" s="0">
-        <v>82.519999999999996</v>
+        <v>77.629999999999995</v>
       </c>
       <c r="J18" s="0">
-        <v>462</v>
+        <v>691</v>
       </c>
       <c r="K18" s="0">
-        <v>1880</v>
+        <v>5260.7200000000003</v>
       </c>
       <c r="L18" s="0">
-        <v>24.73</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="M18" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +966,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>3190002264</v>
+        <v>141095111430</v>
       </c>
       <c r="C19" s="0">
-        <v>3887577792</v>
+        <v>175621247708</v>
       </c>
       <c r="D19" s="0">
-        <v>238209</v>
+        <v>572429</v>
       </c>
       <c r="E19" s="0">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="F19" s="0">
-        <v>84542</v>
+        <v>1096771</v>
       </c>
       <c r="G19" s="0">
-        <v>5.1799999999999997</v>
+        <v>3.5699999999999998</v>
       </c>
       <c r="H19" s="0">
-        <v>10.32</v>
+        <v>9.1799999999999997</v>
       </c>
       <c r="I19" s="0">
-        <v>82.060000000000002</v>
+        <v>80.340000000000003</v>
       </c>
       <c r="J19" s="0">
-        <v>619</v>
+        <v>940</v>
       </c>
       <c r="K19" s="0">
-        <v>1264</v>
+        <v>5594.3000000000002</v>
       </c>
       <c r="L19" s="0">
-        <v>17.02</v>
+        <v>32.829999999999998</v>
       </c>
       <c r="M19" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +1007,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1792509186</v>
+        <v>100743694863</v>
       </c>
       <c r="C20" s="0">
-        <v>2126496854</v>
+        <v>125503888894</v>
       </c>
       <c r="D20" s="0">
-        <v>83523</v>
+        <v>717616</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F20" s="0">
-        <v>148898</v>
+        <v>704193</v>
       </c>
       <c r="G20" s="0">
-        <v>5.8499999999999996</v>
+        <v>4.0300000000000002</v>
       </c>
       <c r="H20" s="0">
-        <v>8.4299999999999997</v>
+        <v>10.91</v>
       </c>
       <c r="I20" s="0">
-        <v>84.290000000000006</v>
+        <v>80.269999999999996</v>
       </c>
       <c r="J20" s="0">
-        <v>286</v>
+        <v>1037</v>
       </c>
       <c r="K20" s="0">
-        <v>1955</v>
+        <v>4617.54</v>
       </c>
       <c r="L20" s="0">
-        <v>39.100000000000001</v>
+        <v>26.859999999999999</v>
       </c>
       <c r="M20" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1048,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>6667124439</v>
+        <v>2396008369</v>
       </c>
       <c r="C21" s="0">
-        <v>8301200126</v>
+        <v>3013422167</v>
       </c>
       <c r="D21" s="0">
-        <v>90992</v>
+        <v>575081</v>
       </c>
       <c r="E21" s="0">
-        <v>72</v>
+        <v>179</v>
       </c>
       <c r="F21" s="0">
-        <v>244872</v>
+        <v>17439</v>
       </c>
       <c r="G21" s="0">
-        <v>2.6800000000000002</v>
+        <v>3.3300000000000001</v>
       </c>
       <c r="H21" s="0">
-        <v>4.7400000000000002</v>
+        <v>8.8900000000000006</v>
       </c>
       <c r="I21" s="0">
-        <v>80.319999999999993</v>
+        <v>79.510000000000005</v>
       </c>
       <c r="J21" s="0">
-        <v>471</v>
+        <v>965</v>
       </c>
       <c r="K21" s="0">
-        <v>2849</v>
+        <v>5244.2399999999998</v>
       </c>
       <c r="L21" s="0">
-        <v>39.640000000000001</v>
+        <v>29.289999999999999</v>
       </c>
       <c r="M21" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="22">
@@ -1050,37 +1089,37 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>10475360625</v>
+        <v>75862941903</v>
       </c>
       <c r="C22" s="0">
-        <v>13371225732</v>
+        <v>91029798477</v>
       </c>
       <c r="D22" s="0">
-        <v>153781</v>
+        <v>665617</v>
       </c>
       <c r="E22" s="0">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="F22" s="0">
-        <v>363631</v>
+        <v>465746</v>
       </c>
       <c r="G22" s="0">
-        <v>4.1799999999999997</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="H22" s="0">
-        <v>7.8499999999999996</v>
+        <v>9.8699999999999992</v>
       </c>
       <c r="I22" s="0">
-        <v>78.340000000000003</v>
+        <v>83.340000000000003</v>
       </c>
       <c r="J22" s="0">
-        <v>491</v>
+        <v>1092</v>
       </c>
       <c r="K22" s="0">
-        <v>1523</v>
+        <v>5403.0299999999997</v>
       </c>
       <c r="L22" s="0">
-        <v>20.32</v>
+        <v>30.210000000000001</v>
       </c>
       <c r="M22" s="0">
         <v>0.080000000000000002</v>
@@ -1091,40 +1130,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>21877001195</v>
+        <v>44959481483</v>
       </c>
       <c r="C23" s="0">
-        <v>27557473645</v>
+        <v>53822582475</v>
       </c>
       <c r="D23" s="0">
-        <v>129670</v>
+        <v>851893</v>
       </c>
       <c r="E23" s="0">
-        <v>68</v>
+        <v>179</v>
       </c>
       <c r="F23" s="0">
-        <v>869483</v>
+        <v>202504</v>
       </c>
       <c r="G23" s="0">
-        <v>4.0899999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="H23" s="0">
-        <v>7.04</v>
+        <v>11.949999999999999</v>
       </c>
       <c r="I23" s="0">
-        <v>79.390000000000001</v>
+        <v>83.530000000000001</v>
       </c>
       <c r="J23" s="0">
-        <v>459</v>
+        <v>1489</v>
       </c>
       <c r="K23" s="0">
-        <v>1627</v>
+        <v>4567.8999999999996</v>
       </c>
       <c r="L23" s="0">
-        <v>23.82</v>
+        <v>25.579999999999998</v>
       </c>
       <c r="M23" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1132,40 +1171,573 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
+        <v>25260217147</v>
+      </c>
+      <c r="C24" s="0">
+        <v>29815902585</v>
+      </c>
+      <c r="D24" s="0">
+        <v>685896</v>
+      </c>
+      <c r="E24" s="0">
+        <v>185</v>
+      </c>
+      <c r="F24" s="0">
+        <v>128824</v>
+      </c>
+      <c r="G24" s="0">
+        <v>2.96</v>
+      </c>
+      <c r="H24" s="0">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="I24" s="0">
+        <v>84.719999999999999</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1269</v>
+      </c>
+      <c r="K24" s="0">
+        <v>6456.8699999999999</v>
+      </c>
+      <c r="L24" s="0">
+        <v>35.289999999999999</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.089999999999999997</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>8968582690</v>
+      </c>
+      <c r="C25" s="0">
+        <v>10484481345</v>
+      </c>
+      <c r="D25" s="0">
+        <v>783594</v>
+      </c>
+      <c r="E25" s="0">
+        <v>234</v>
+      </c>
+      <c r="F25" s="0">
+        <v>31306</v>
+      </c>
+      <c r="G25" s="0">
+        <v>2.3399999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>8.3399999999999999</v>
+      </c>
+      <c r="I25" s="0">
+        <v>85.540000000000006</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1431</v>
+      </c>
+      <c r="K25" s="0">
+        <v>7143.7200000000003</v>
+      </c>
+      <c r="L25" s="0">
+        <v>30.530000000000001</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>24029953548</v>
+      </c>
+      <c r="C26" s="0">
+        <v>28854891286</v>
+      </c>
+      <c r="D26" s="0">
+        <v>1050415</v>
+      </c>
+      <c r="E26" s="0">
+        <v>200</v>
+      </c>
+      <c r="F26" s="0">
+        <v>44495</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.6200000000000001</v>
+      </c>
+      <c r="H26" s="0">
+        <v>11.539999999999999</v>
+      </c>
+      <c r="I26" s="0">
+        <v>83.280000000000001</v>
+      </c>
+      <c r="J26" s="0">
+        <v>3275</v>
+      </c>
+      <c r="K26" s="0">
+        <v>8005.2799999999997</v>
+      </c>
+      <c r="L26" s="0">
+        <v>40.409999999999997</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.087999999999999995</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>15131188759</v>
+      </c>
+      <c r="C27" s="0">
+        <v>17776006022</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1333534</v>
+      </c>
+      <c r="E27" s="0">
+        <v>234</v>
+      </c>
+      <c r="F27" s="0">
+        <v>20743</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1.5600000000000001</v>
+      </c>
+      <c r="H27" s="0">
+        <v>12.17</v>
+      </c>
+      <c r="I27" s="0">
+        <v>85.120000000000005</v>
+      </c>
+      <c r="J27" s="0">
+        <v>3670</v>
+      </c>
+      <c r="K27" s="0">
+        <v>8959.0699999999997</v>
+      </c>
+      <c r="L27" s="0">
+        <v>38.369999999999997</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.082000000000000003</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>15814930907</v>
+      </c>
+      <c r="C28" s="0">
+        <v>19286103769</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1513823</v>
+      </c>
+      <c r="E28" s="0">
+        <v>263</v>
+      </c>
+      <c r="F28" s="0">
+        <v>21804</v>
+      </c>
+      <c r="G28" s="0">
+        <v>1.71</v>
+      </c>
+      <c r="H28" s="0">
+        <v>12.369999999999999</v>
+      </c>
+      <c r="I28" s="0">
+        <v>82</v>
+      </c>
+      <c r="J28" s="0">
+        <v>3401</v>
+      </c>
+      <c r="K28" s="0">
+        <v>8716.1100000000006</v>
+      </c>
+      <c r="L28" s="0">
+        <v>33.469999999999999</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>17469108193</v>
+      </c>
+      <c r="C29" s="0">
+        <v>20300270014</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1819021</v>
+      </c>
+      <c r="E29" s="0">
+        <v>282</v>
+      </c>
+      <c r="F29" s="0">
+        <v>17720</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.5900000000000001</v>
+      </c>
+      <c r="H29" s="0">
+        <v>13.49</v>
+      </c>
+      <c r="I29" s="0">
+        <v>86.049999999999997</v>
+      </c>
+      <c r="J29" s="0">
+        <v>4065</v>
+      </c>
+      <c r="K29" s="0">
+        <v>9146.3400000000001</v>
+      </c>
+      <c r="L29" s="0">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.068000000000000005</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>21222815617</v>
+      </c>
+      <c r="C30" s="0">
+        <v>25117527286</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1747914</v>
+      </c>
+      <c r="E30" s="0">
+        <v>281</v>
+      </c>
+      <c r="F30" s="0">
+        <v>20281</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.4099999999999999</v>
+      </c>
+      <c r="H30" s="0">
+        <v>12.91</v>
+      </c>
+      <c r="I30" s="0">
+        <v>84.489999999999995</v>
+      </c>
+      <c r="J30" s="0">
+        <v>4409</v>
+      </c>
+      <c r="K30" s="0">
+        <v>9415.2399999999998</v>
+      </c>
+      <c r="L30" s="0">
+        <v>33.520000000000003</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.070000000000000007</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>22569392688</v>
+      </c>
+      <c r="C31" s="0">
+        <v>27024216560</v>
+      </c>
+      <c r="D31" s="0">
+        <v>2004764</v>
+      </c>
+      <c r="E31" s="0">
+        <v>298</v>
+      </c>
+      <c r="F31" s="0">
+        <v>16120</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H31" s="0">
+        <v>13.56</v>
+      </c>
+      <c r="I31" s="0">
+        <v>83.519999999999996</v>
+      </c>
+      <c r="J31" s="0">
+        <v>5677</v>
+      </c>
+      <c r="K31" s="0">
+        <v>9834.1200000000008</v>
+      </c>
+      <c r="L31" s="0">
+        <v>33.289999999999999</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>20432577455</v>
+      </c>
+      <c r="C32" s="0">
+        <v>23576275957</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1322281</v>
+      </c>
+      <c r="E32" s="0">
+        <v>236</v>
+      </c>
+      <c r="F32" s="0">
+        <v>24357</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.3700000000000001</v>
+      </c>
+      <c r="H32" s="0">
+        <v>11.359999999999999</v>
+      </c>
+      <c r="I32" s="0">
+        <v>86.670000000000002</v>
+      </c>
+      <c r="J32" s="0">
+        <v>4101</v>
+      </c>
+      <c r="K32" s="0">
+        <v>11785.01</v>
+      </c>
+      <c r="L32" s="0">
+        <v>49.939999999999998</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>40079698492</v>
+      </c>
+      <c r="C33" s="0">
+        <v>48898013180</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1914566</v>
+      </c>
+      <c r="E33" s="0">
+        <v>267</v>
+      </c>
+      <c r="F33" s="0">
+        <v>34923</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.3700000000000001</v>
+      </c>
+      <c r="H33" s="0">
+        <v>14.42</v>
+      </c>
+      <c r="I33" s="0">
+        <v>81.969999999999999</v>
+      </c>
+      <c r="J33" s="0">
+        <v>5279</v>
+      </c>
+      <c r="K33" s="0">
+        <v>10076.57</v>
+      </c>
+      <c r="L33" s="0">
+        <v>37.960000000000001</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.075999999999999998</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>13507941855</v>
+      </c>
+      <c r="C34" s="0">
+        <v>15801941838</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1894717</v>
+      </c>
+      <c r="E34" s="0">
+        <v>318</v>
+      </c>
+      <c r="F34" s="0">
+        <v>11097</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.3300000000000001</v>
+      </c>
+      <c r="H34" s="0">
+        <v>11.970000000000001</v>
+      </c>
+      <c r="I34" s="0">
+        <v>85.480000000000004</v>
+      </c>
+      <c r="J34" s="0">
+        <v>4478</v>
+      </c>
+      <c r="K34" s="0">
+        <v>10787.83</v>
+      </c>
+      <c r="L34" s="0">
+        <v>33.920000000000002</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.068000000000000005</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>58819153428</v>
+      </c>
+      <c r="C35" s="0">
+        <v>71140436234</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1617196</v>
+      </c>
+      <c r="E35" s="0">
+        <v>296</v>
+      </c>
+      <c r="F35" s="0">
+        <v>61721</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="H35" s="0">
+        <v>11.6</v>
+      </c>
+      <c r="I35" s="0">
+        <v>82.680000000000007</v>
+      </c>
+      <c r="J35" s="0">
+        <v>4028</v>
+      </c>
+      <c r="K35" s="0">
+        <v>11862.030000000001</v>
+      </c>
+      <c r="L35" s="0">
+        <v>41.329999999999998</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.085000000000000006</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>25106726688</v>
+      </c>
+      <c r="C36" s="0">
+        <v>31026338195</v>
+      </c>
+      <c r="D36" s="0">
+        <v>2029192</v>
+      </c>
+      <c r="E36" s="0">
+        <v>327</v>
+      </c>
+      <c r="F36" s="0">
+        <v>19655</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.29</v>
+      </c>
+      <c r="H36" s="0">
+        <v>12.390000000000001</v>
+      </c>
+      <c r="I36" s="0">
+        <v>80.920000000000002</v>
+      </c>
+      <c r="J36" s="0">
+        <v>4793</v>
+      </c>
+      <c r="K36" s="0">
+        <v>13689.07</v>
+      </c>
+      <c r="L36" s="0">
+        <v>41.600000000000001</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.084000000000000005</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
         <v>1131445254792</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C37" s="0">
         <v>1380192482862</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D37" s="0">
         <v>543655</v>
       </c>
-      <c r="E24" s="0">
+      <c r="E37" s="0">
         <v>141</v>
       </c>
-      <c r="F24" s="0">
+      <c r="F37" s="0">
         <v>8622704</v>
       </c>
-      <c r="G24" s="0">
+      <c r="G37" s="0">
         <v>3.3999999999999999</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H37" s="0">
         <v>8.7799999999999994</v>
       </c>
-      <c r="I24" s="0">
+      <c r="I37" s="0">
         <v>81.980000000000004</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J37" s="0">
         <v>938</v>
       </c>
-      <c r="K24" s="0">
-        <v>5236</v>
-      </c>
-      <c r="L24" s="0">
+      <c r="K37" s="0">
+        <v>5235.6700000000001</v>
+      </c>
+      <c r="L37" s="0">
         <v>32.57</v>
       </c>
-      <c r="M24" s="0">
-        <v>0.080000000000000002</v>
+      <c r="M37" s="0">
+        <v>0.085000000000000006</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Aircraft_Cumulative_Statistics_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Aircraft_Cumulative_Statistics_2025.xlsx
@@ -30,7 +30,7 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -925,19 +925,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>51233067668</v>
+        <v>52004117641</v>
       </c>
       <c r="C18" s="0">
-        <v>65999534459</v>
+        <v>67021630293</v>
       </c>
       <c r="D18" s="0">
-        <v>468447</v>
+        <v>468290</v>
       </c>
       <c r="E18" s="0">
         <v>141</v>
       </c>
       <c r="F18" s="0">
-        <v>676781</v>
+        <v>687113</v>
       </c>
       <c r="G18" s="0">
         <v>4.7999999999999998</v>
@@ -946,16 +946,16 @@
         <v>9.4700000000000006</v>
       </c>
       <c r="I18" s="0">
-        <v>77.629999999999995</v>
+        <v>77.590000000000003</v>
       </c>
       <c r="J18" s="0">
         <v>691</v>
       </c>
       <c r="K18" s="0">
-        <v>5260.7200000000003</v>
+        <v>5248.7799999999997</v>
       </c>
       <c r="L18" s="0">
-        <v>37.299999999999997</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="M18" s="0">
         <v>0.106</v>
@@ -966,37 +966,37 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>141095111430</v>
+        <v>142548664923</v>
       </c>
       <c r="C19" s="0">
-        <v>175621247708</v>
+        <v>177613711745</v>
       </c>
       <c r="D19" s="0">
-        <v>572429</v>
+        <v>572025</v>
       </c>
       <c r="E19" s="0">
         <v>171</v>
       </c>
       <c r="F19" s="0">
-        <v>1096771</v>
+        <v>1108286</v>
       </c>
       <c r="G19" s="0">
         <v>3.5699999999999998</v>
       </c>
       <c r="H19" s="0">
-        <v>9.1799999999999997</v>
+        <v>9.1699999999999999</v>
       </c>
       <c r="I19" s="0">
-        <v>80.340000000000003</v>
+        <v>80.260000000000005</v>
       </c>
       <c r="J19" s="0">
         <v>940</v>
       </c>
       <c r="K19" s="0">
-        <v>5594.3000000000002</v>
+        <v>5589.2399999999998</v>
       </c>
       <c r="L19" s="0">
-        <v>32.829999999999998</v>
+        <v>32.770000000000003</v>
       </c>
       <c r="M19" s="0">
         <v>0.089999999999999997</v>
@@ -1704,19 +1704,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>1131445254792</v>
+        <v>1133669858258</v>
       </c>
       <c r="C37" s="0">
-        <v>1380192482862</v>
+        <v>1383207042733</v>
       </c>
       <c r="D37" s="0">
-        <v>543655</v>
+        <v>543572</v>
       </c>
       <c r="E37" s="0">
         <v>141</v>
       </c>
       <c r="F37" s="0">
-        <v>8622704</v>
+        <v>8644551</v>
       </c>
       <c r="G37" s="0">
         <v>3.3999999999999999</v>
@@ -1725,16 +1725,16 @@
         <v>8.7799999999999994</v>
       </c>
       <c r="I37" s="0">
-        <v>81.980000000000004</v>
+        <v>81.959999999999994</v>
       </c>
       <c r="J37" s="0">
         <v>938</v>
       </c>
       <c r="K37" s="0">
-        <v>5235.6700000000001</v>
+        <v>5234.79</v>
       </c>
       <c r="L37" s="0">
-        <v>32.57</v>
+        <v>32.560000000000002</v>
       </c>
       <c r="M37" s="0">
         <v>0.085000000000000006</v>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Aircraft_Cumulative_Statistics_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2025/Aircraft_Cumulative_Statistics_2025.xlsx
@@ -13,35 +13,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>E145</t>
-  </si>
-  <si>
-    <t>CRJ-200</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
-    <t>E175</t>
-  </si>
-  <si>
-    <t>CRJ-550</t>
-  </si>
-  <si>
-    <t>CRJ-700</t>
-  </si>
-  <si>
-    <t>E190</t>
-  </si>
-  <si>
-    <t>CRJ-900</t>
-  </si>
-  <si>
     <t>A220-100</t>
   </si>
   <si>
@@ -52,9 +28,6 @@
   </si>
   <si>
     <t>A320</t>
-  </si>
-  <si>
-    <t>A320NEO</t>
   </si>
   <si>
     <t>A321</t>
@@ -205,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -228,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="L1" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="M1" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="K1" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="M1" s="0" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -269,40 +242,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>3120944830</v>
+        <v>4196143473</v>
       </c>
       <c r="C2" s="0">
-        <v>3695825554</v>
+        <v>5111581351</v>
       </c>
       <c r="D2" s="0">
-        <v>79276</v>
+        <v>315530</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F2" s="0">
-        <v>233231</v>
+        <v>50553</v>
       </c>
       <c r="G2" s="0">
-        <v>5</v>
+        <v>3.1200000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>7.3799999999999999</v>
+        <v>8.2599999999999998</v>
       </c>
       <c r="I2" s="0">
-        <v>84.450000000000003</v>
+        <v>82.090000000000003</v>
       </c>
       <c r="J2" s="0">
-        <v>317</v>
+        <v>928</v>
       </c>
       <c r="K2" s="0">
-        <v>1830.75</v>
+        <v>4985.6499999999996</v>
       </c>
       <c r="L2" s="0">
-        <v>36.619999999999997</v>
+        <v>45.75</v>
       </c>
       <c r="M2" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -310,40 +283,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>1562581593</v>
+        <v>4731343011</v>
       </c>
       <c r="C3" s="0">
-        <v>2109008000</v>
+        <v>5750325243</v>
       </c>
       <c r="D3" s="0">
-        <v>44806</v>
+        <v>482815</v>
       </c>
       <c r="E3" s="0">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F3" s="0">
-        <v>128998</v>
+        <v>40027</v>
       </c>
       <c r="G3" s="0">
-        <v>2.7400000000000002</v>
+        <v>3.3599999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>4.0899999999999999</v>
+        <v>10.02</v>
       </c>
       <c r="I3" s="0">
-        <v>74.090000000000003</v>
+        <v>82.280000000000001</v>
       </c>
       <c r="J3" s="0">
-        <v>327</v>
+        <v>1105</v>
       </c>
       <c r="K3" s="0">
-        <v>2069.23</v>
+        <v>5146.0900000000001</v>
       </c>
       <c r="L3" s="0">
-        <v>41.380000000000003</v>
+        <v>39.590000000000003</v>
       </c>
       <c r="M3" s="0">
-        <v>0.189</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="4">
@@ -351,40 +324,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>2200181667</v>
+        <v>27860553412</v>
       </c>
       <c r="C4" s="0">
-        <v>2709362587</v>
+        <v>34250170083</v>
       </c>
       <c r="D4" s="0">
-        <v>44365</v>
+        <v>349849</v>
       </c>
       <c r="E4" s="0">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="F4" s="0">
-        <v>100184</v>
+        <v>369969</v>
       </c>
       <c r="G4" s="0">
-        <v>1.6399999999999999</v>
+        <v>3.7799999999999998</v>
       </c>
       <c r="H4" s="0">
-        <v>2.7000000000000002</v>
+        <v>8.2300000000000004</v>
       </c>
       <c r="I4" s="0">
-        <v>81.209999999999994</v>
+        <v>81.340000000000003</v>
       </c>
       <c r="J4" s="0">
-        <v>411</v>
+        <v>721</v>
       </c>
       <c r="K4" s="0">
-        <v>1787.53</v>
+        <v>4943.9499999999998</v>
       </c>
       <c r="L4" s="0">
-        <v>27.149999999999999</v>
+        <v>38.539999999999999</v>
       </c>
       <c r="M4" s="0">
-        <v>0.109</v>
+        <v>0.11600000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -392,40 +365,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>39244051208</v>
+        <v>22469827691</v>
       </c>
       <c r="C5" s="0">
-        <v>48807922861</v>
+        <v>27775715408</v>
       </c>
       <c r="D5" s="0">
-        <v>142359</v>
+        <v>439072</v>
       </c>
       <c r="E5" s="0">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="F5" s="0">
-        <v>1242759</v>
+        <v>229674</v>
       </c>
       <c r="G5" s="0">
-        <v>3.6200000000000001</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="H5" s="0">
-        <v>6.71</v>
+        <v>8.3499999999999996</v>
       </c>
       <c r="I5" s="0">
-        <v>80.409999999999997</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="J5" s="0">
-        <v>524</v>
+        <v>794</v>
       </c>
       <c r="K5" s="0">
-        <v>1538.8199999999999</v>
+        <v>5499.7200000000003</v>
       </c>
       <c r="L5" s="0">
-        <v>20.559999999999999</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="M5" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="6">
@@ -433,40 +406,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>1731201783</v>
+        <v>75525670350</v>
       </c>
       <c r="C6" s="0">
-        <v>2151823450</v>
+        <v>89373722447</v>
       </c>
       <c r="D6" s="0">
-        <v>63345</v>
+        <v>713848</v>
       </c>
       <c r="E6" s="0">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="F6" s="0">
-        <v>123689</v>
+        <v>445016</v>
       </c>
       <c r="G6" s="0">
-        <v>3.6400000000000001</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="H6" s="0">
-        <v>5.6399999999999997</v>
+        <v>10.289999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>80.450000000000003</v>
+        <v>84.510000000000005</v>
       </c>
       <c r="J6" s="0">
-        <v>348</v>
+        <v>1089</v>
       </c>
       <c r="K6" s="0">
-        <v>2097.0900000000001</v>
+        <v>6274.1499999999996</v>
       </c>
       <c r="L6" s="0">
-        <v>41.939999999999998</v>
+        <v>33.880000000000003</v>
       </c>
       <c r="M6" s="0">
-        <v>0.187</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="7">
@@ -474,40 +447,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>6422303636</v>
+        <v>57283031634</v>
       </c>
       <c r="C7" s="0">
-        <v>8124646224</v>
+        <v>67192254611</v>
       </c>
       <c r="D7" s="0">
-        <v>98936</v>
+        <v>926023</v>
       </c>
       <c r="E7" s="0">
-        <v>66</v>
+        <v>196</v>
       </c>
       <c r="F7" s="0">
-        <v>278194</v>
+        <v>209569</v>
       </c>
       <c r="G7" s="0">
-        <v>3.3900000000000001</v>
+        <v>2.8900000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>5.7400000000000002</v>
+        <v>11.539999999999999</v>
       </c>
       <c r="I7" s="0">
-        <v>79.049999999999997</v>
+        <v>85.25</v>
       </c>
       <c r="J7" s="0">
-        <v>444</v>
+        <v>1639</v>
       </c>
       <c r="K7" s="0">
-        <v>2337.5799999999999</v>
+        <v>6082.8199999999997</v>
       </c>
       <c r="L7" s="0">
-        <v>35.560000000000002</v>
+        <v>31.09</v>
       </c>
       <c r="M7" s="0">
-        <v>0.13600000000000001</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="8">
@@ -515,40 +488,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>715214100</v>
+        <v>5377494974</v>
       </c>
       <c r="C8" s="0">
-        <v>915843610</v>
+        <v>6451110233</v>
       </c>
       <c r="D8" s="0">
-        <v>131966</v>
+        <v>223997</v>
       </c>
       <c r="E8" s="0">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F8" s="0">
-        <v>18623</v>
+        <v>138151</v>
       </c>
       <c r="G8" s="0">
-        <v>2.6800000000000002</v>
+        <v>4.7999999999999998</v>
       </c>
       <c r="H8" s="0">
-        <v>4.5199999999999996</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>78.090000000000003</v>
+        <v>83.359999999999999</v>
       </c>
       <c r="J8" s="0">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="K8" s="0">
-        <v>7281.5299999999997</v>
+        <v>5079.3500000000004</v>
       </c>
       <c r="L8" s="0">
-        <v>71</v>
+        <v>46.18</v>
       </c>
       <c r="M8" s="0">
-        <v>0.249</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="9">
@@ -556,40 +529,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>12064589320</v>
+        <v>4343703745</v>
       </c>
       <c r="C9" s="0">
-        <v>15021992569</v>
+        <v>5252432220</v>
       </c>
       <c r="D9" s="0">
-        <v>136464</v>
+        <v>362737</v>
       </c>
       <c r="E9" s="0">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="F9" s="0">
-        <v>439981</v>
+        <v>47805</v>
       </c>
       <c r="G9" s="0">
-        <v>4</v>
+        <v>3.2999999999999998</v>
       </c>
       <c r="H9" s="0">
-        <v>6.8200000000000003</v>
+        <v>8.4399999999999995</v>
       </c>
       <c r="I9" s="0">
-        <v>80.310000000000002</v>
+        <v>82.700000000000003</v>
       </c>
       <c r="J9" s="0">
-        <v>454</v>
+        <v>872</v>
       </c>
       <c r="K9" s="0">
-        <v>2159.73</v>
+        <v>8528.4099999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>28.699999999999999</v>
+        <v>67.689999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.108</v>
+        <v>0.19800000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -597,40 +570,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>4196143473</v>
+        <v>85612907499</v>
       </c>
       <c r="C10" s="0">
-        <v>5111581351</v>
+        <v>104429364546</v>
       </c>
       <c r="D10" s="0">
-        <v>315530</v>
+        <v>551428</v>
       </c>
       <c r="E10" s="0">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F10" s="0">
-        <v>50553</v>
+        <v>648100</v>
       </c>
       <c r="G10" s="0">
-        <v>3.1200000000000001</v>
+        <v>3.4199999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>8.2599999999999998</v>
+        <v>9.0899999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>82.090000000000003</v>
+        <v>81.980000000000004</v>
       </c>
       <c r="J10" s="0">
-        <v>928</v>
+        <v>955</v>
       </c>
       <c r="K10" s="0">
-        <v>4985.6499999999996</v>
+        <v>5740.2200000000003</v>
       </c>
       <c r="L10" s="0">
-        <v>45.75</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>0.13100000000000001</v>
+        <v>0.095000000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -638,40 +611,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>15882915527</v>
+        <v>44204921930</v>
       </c>
       <c r="C11" s="0">
-        <v>19809443626</v>
+        <v>53335041214</v>
       </c>
       <c r="D11" s="0">
-        <v>447772</v>
+        <v>761494</v>
       </c>
       <c r="E11" s="0">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="F11" s="0">
-        <v>158596</v>
+        <v>237195</v>
       </c>
       <c r="G11" s="0">
-        <v>3.5800000000000001</v>
+        <v>3.3900000000000001</v>
       </c>
       <c r="H11" s="0">
-        <v>9.3800000000000008</v>
+        <v>11.550000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>80.180000000000007</v>
+        <v>82.879999999999995</v>
       </c>
       <c r="J11" s="0">
-        <v>919</v>
+        <v>1337</v>
       </c>
       <c r="K11" s="0">
-        <v>5050.1999999999998</v>
+        <v>5020.2399999999998</v>
       </c>
       <c r="L11" s="0">
-        <v>37.109999999999999</v>
+        <v>29.84</v>
       </c>
       <c r="M11" s="0">
-        <v>0.106</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -679,40 +652,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>31319540146</v>
+        <v>1900273733</v>
       </c>
       <c r="C12" s="0">
-        <v>38454560061</v>
+        <v>2405533207</v>
       </c>
       <c r="D12" s="0">
-        <v>351633</v>
+        <v>552996</v>
       </c>
       <c r="E12" s="0">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="F12" s="0">
-        <v>402609</v>
+        <v>13685</v>
       </c>
       <c r="G12" s="0">
-        <v>3.6800000000000002</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="H12" s="0">
-        <v>8.0399999999999991</v>
+        <v>8.4900000000000002</v>
       </c>
       <c r="I12" s="0">
-        <v>81.450000000000003</v>
+        <v>79</v>
       </c>
       <c r="J12" s="0">
-        <v>730</v>
+        <v>982</v>
       </c>
       <c r="K12" s="0">
-        <v>4956.46</v>
+        <v>5768.4499999999998</v>
       </c>
       <c r="L12" s="0">
-        <v>37.950000000000003</v>
+        <v>32.229999999999997</v>
       </c>
       <c r="M12" s="0">
-        <v>0.113</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="13">
@@ -720,40 +693,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>66911351659</v>
+        <v>57259254797</v>
       </c>
       <c r="C13" s="0">
-        <v>82401204498</v>
+        <v>68625399141</v>
       </c>
       <c r="D13" s="0">
-        <v>494813</v>
+        <v>635891</v>
       </c>
       <c r="E13" s="0">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="F13" s="0">
-        <v>547446</v>
+        <v>379947</v>
       </c>
       <c r="G13" s="0">
-        <v>3.29</v>
+        <v>3.52</v>
       </c>
       <c r="H13" s="0">
-        <v>8.3699999999999992</v>
+        <v>9.5700000000000003</v>
       </c>
       <c r="I13" s="0">
-        <v>81.200000000000003</v>
+        <v>83.439999999999998</v>
       </c>
       <c r="J13" s="0">
-        <v>922</v>
+        <v>1008</v>
       </c>
       <c r="K13" s="0">
-        <v>5611.25</v>
+        <v>5498.6400000000003</v>
       </c>
       <c r="L13" s="0">
-        <v>34.439999999999998</v>
+        <v>30.699999999999999</v>
       </c>
       <c r="M13" s="0">
-        <v>0.095000000000000001</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="14">
@@ -761,40 +734,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>23750015633</v>
+        <v>24787095633</v>
       </c>
       <c r="C14" s="0">
-        <v>29514200404</v>
+        <v>29569747301</v>
       </c>
       <c r="D14" s="0">
-        <v>536134</v>
+        <v>847514</v>
       </c>
       <c r="E14" s="0">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F14" s="0">
-        <v>176467</v>
+        <v>116718</v>
       </c>
       <c r="G14" s="0">
-        <v>3.21</v>
+        <v>3.3500000000000001</v>
       </c>
       <c r="H14" s="0">
-        <v>8.2899999999999991</v>
+        <v>12</v>
       </c>
       <c r="I14" s="0">
-        <v>80.469999999999999</v>
+        <v>83.829999999999998</v>
       </c>
       <c r="J14" s="0">
-        <v>921</v>
+        <v>1415</v>
       </c>
       <c r="K14" s="0">
-        <v>4666.3699999999999</v>
+        <v>4936.1000000000004</v>
       </c>
       <c r="L14" s="0">
-        <v>25.66</v>
+        <v>27.579999999999998</v>
       </c>
       <c r="M14" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.070000000000000007</v>
       </c>
     </row>
     <row r="15">
@@ -802,40 +775,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>101016757403</v>
+        <v>25260217147</v>
       </c>
       <c r="C15" s="0">
-        <v>120700316516</v>
+        <v>29815902585</v>
       </c>
       <c r="D15" s="0">
-        <v>729969</v>
+        <v>685896</v>
       </c>
       <c r="E15" s="0">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F15" s="0">
-        <v>557701</v>
+        <v>128824</v>
       </c>
       <c r="G15" s="0">
-        <v>3.3700000000000001</v>
+        <v>2.96</v>
       </c>
       <c r="H15" s="0">
-        <v>10.289999999999999</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="I15" s="0">
-        <v>83.689999999999998</v>
+        <v>84.719999999999999</v>
       </c>
       <c r="J15" s="0">
-        <v>1165</v>
+        <v>1269</v>
       </c>
       <c r="K15" s="0">
-        <v>5951.0900000000001</v>
+        <v>6456.8699999999999</v>
       </c>
       <c r="L15" s="0">
-        <v>31.84</v>
+        <v>35.289999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.084000000000000005</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="16">
@@ -843,40 +816,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>90493835556</v>
+        <v>8968582690</v>
       </c>
       <c r="C16" s="0">
-        <v>109179795315</v>
+        <v>10484481345</v>
       </c>
       <c r="D16" s="0">
-        <v>857052</v>
+        <v>783594</v>
       </c>
       <c r="E16" s="0">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="F16" s="0">
-        <v>356273</v>
+        <v>31306</v>
       </c>
       <c r="G16" s="0">
-        <v>2.7999999999999998</v>
+        <v>2.3399999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>10.58</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="I16" s="0">
-        <v>82.890000000000001</v>
+        <v>85.540000000000006</v>
       </c>
       <c r="J16" s="0">
-        <v>1534</v>
+        <v>1431</v>
       </c>
       <c r="K16" s="0">
-        <v>5816</v>
+        <v>7143.7200000000003</v>
       </c>
       <c r="L16" s="0">
-        <v>28.91</v>
+        <v>30.530000000000001</v>
       </c>
       <c r="M16" s="0">
-        <v>0.071999999999999995</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="17">
@@ -884,40 +857,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>6111034075</v>
+        <v>24029953548</v>
       </c>
       <c r="C17" s="0">
-        <v>7392077785</v>
+        <v>28854891286</v>
       </c>
       <c r="D17" s="0">
-        <v>206829</v>
+        <v>1050415</v>
       </c>
       <c r="E17" s="0">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="F17" s="0">
-        <v>190920</v>
+        <v>44495</v>
       </c>
       <c r="G17" s="0">
-        <v>5.3399999999999999</v>
+        <v>1.6200000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>6.8399999999999999</v>
+        <v>11.539999999999999</v>
       </c>
       <c r="I17" s="0">
-        <v>82.670000000000002</v>
+        <v>83.280000000000001</v>
       </c>
       <c r="J17" s="0">
-        <v>346</v>
+        <v>3275</v>
       </c>
       <c r="K17" s="0">
-        <v>5128.9300000000003</v>
+        <v>8005.2799999999997</v>
       </c>
       <c r="L17" s="0">
-        <v>45.399999999999999</v>
+        <v>40.409999999999997</v>
       </c>
       <c r="M17" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="18">
@@ -925,40 +898,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>52004117641</v>
+        <v>15131188759</v>
       </c>
       <c r="C18" s="0">
-        <v>67021630293</v>
+        <v>17776006022</v>
       </c>
       <c r="D18" s="0">
-        <v>468290</v>
+        <v>1333534</v>
       </c>
       <c r="E18" s="0">
-        <v>141</v>
+        <v>234</v>
       </c>
       <c r="F18" s="0">
-        <v>687113</v>
+        <v>20743</v>
       </c>
       <c r="G18" s="0">
-        <v>4.7999999999999998</v>
+        <v>1.5600000000000001</v>
       </c>
       <c r="H18" s="0">
-        <v>9.4700000000000006</v>
+        <v>12.17</v>
       </c>
       <c r="I18" s="0">
-        <v>77.590000000000003</v>
+        <v>85.120000000000005</v>
       </c>
       <c r="J18" s="0">
-        <v>691</v>
+        <v>3670</v>
       </c>
       <c r="K18" s="0">
-        <v>5248.7799999999997</v>
+        <v>8959.0699999999997</v>
       </c>
       <c r="L18" s="0">
-        <v>37.200000000000003</v>
+        <v>38.369999999999997</v>
       </c>
       <c r="M18" s="0">
-        <v>0.106</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="19">
@@ -966,40 +939,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>142548664923</v>
+        <v>4268775210</v>
       </c>
       <c r="C19" s="0">
-        <v>177613711745</v>
+        <v>5236576465</v>
       </c>
       <c r="D19" s="0">
-        <v>572025</v>
+        <v>1319037</v>
       </c>
       <c r="E19" s="0">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="F19" s="0">
-        <v>1108286</v>
+        <v>5766</v>
       </c>
       <c r="G19" s="0">
-        <v>3.5699999999999998</v>
+        <v>1.45</v>
       </c>
       <c r="H19" s="0">
-        <v>9.1699999999999999</v>
+        <v>12.390000000000001</v>
       </c>
       <c r="I19" s="0">
-        <v>80.260000000000005</v>
+        <v>81.519999999999996</v>
       </c>
       <c r="J19" s="0">
-        <v>940</v>
+        <v>4094</v>
       </c>
       <c r="K19" s="0">
-        <v>5589.2399999999998</v>
+        <v>9019.0799999999999</v>
       </c>
       <c r="L19" s="0">
-        <v>32.770000000000003</v>
+        <v>40.659999999999997</v>
       </c>
       <c r="M19" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="20">
@@ -1007,40 +980,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>100743694863</v>
+        <v>17469108193</v>
       </c>
       <c r="C20" s="0">
-        <v>125503888894</v>
+        <v>20300270014</v>
       </c>
       <c r="D20" s="0">
-        <v>717616</v>
+        <v>1819021</v>
       </c>
       <c r="E20" s="0">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="F20" s="0">
-        <v>704193</v>
+        <v>17720</v>
       </c>
       <c r="G20" s="0">
-        <v>4.0300000000000002</v>
+        <v>1.5900000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>10.91</v>
+        <v>13.49</v>
       </c>
       <c r="I20" s="0">
-        <v>80.269999999999996</v>
+        <v>86.049999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>1037</v>
+        <v>4065</v>
       </c>
       <c r="K20" s="0">
-        <v>4617.54</v>
+        <v>9146.3400000000001</v>
       </c>
       <c r="L20" s="0">
-        <v>26.859999999999999</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="M20" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="21">
@@ -1048,40 +1021,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>2396008369</v>
+        <v>21222815617</v>
       </c>
       <c r="C21" s="0">
-        <v>3013422167</v>
+        <v>25117527286</v>
       </c>
       <c r="D21" s="0">
-        <v>575081</v>
+        <v>1932117</v>
       </c>
       <c r="E21" s="0">
-        <v>179</v>
+        <v>281</v>
       </c>
       <c r="F21" s="0">
-        <v>17439</v>
+        <v>20281</v>
       </c>
       <c r="G21" s="0">
-        <v>3.3300000000000001</v>
+        <v>1.5600000000000001</v>
       </c>
       <c r="H21" s="0">
-        <v>8.8900000000000006</v>
+        <v>14.279999999999999</v>
       </c>
       <c r="I21" s="0">
-        <v>79.510000000000005</v>
+        <v>84.489999999999995</v>
       </c>
       <c r="J21" s="0">
-        <v>965</v>
+        <v>4409</v>
       </c>
       <c r="K21" s="0">
-        <v>5244.2399999999998</v>
+        <v>8712.9500000000007</v>
       </c>
       <c r="L21" s="0">
-        <v>29.289999999999999</v>
+        <v>31.02</v>
       </c>
       <c r="M21" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.064000000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1089,40 +1062,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>75862941903</v>
+        <v>22569392688</v>
       </c>
       <c r="C22" s="0">
-        <v>91029798477</v>
+        <v>27024216560</v>
       </c>
       <c r="D22" s="0">
-        <v>665617</v>
+        <v>2004764</v>
       </c>
       <c r="E22" s="0">
-        <v>179</v>
+        <v>298</v>
       </c>
       <c r="F22" s="0">
-        <v>465746</v>
+        <v>16120</v>
       </c>
       <c r="G22" s="0">
-        <v>3.4100000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="H22" s="0">
-        <v>9.8699999999999992</v>
+        <v>13.56</v>
       </c>
       <c r="I22" s="0">
-        <v>83.340000000000003</v>
+        <v>83.519999999999996</v>
       </c>
       <c r="J22" s="0">
-        <v>1092</v>
+        <v>5677</v>
       </c>
       <c r="K22" s="0">
-        <v>5403.0299999999997</v>
+        <v>9834.1200000000008</v>
       </c>
       <c r="L22" s="0">
-        <v>30.210000000000001</v>
+        <v>33.289999999999999</v>
       </c>
       <c r="M22" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="23">
@@ -1130,40 +1103,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>44959481483</v>
+        <v>20432577455</v>
       </c>
       <c r="C23" s="0">
-        <v>53822582475</v>
+        <v>23576275957</v>
       </c>
       <c r="D23" s="0">
-        <v>851893</v>
+        <v>1322281</v>
       </c>
       <c r="E23" s="0">
-        <v>179</v>
+        <v>236</v>
       </c>
       <c r="F23" s="0">
-        <v>202504</v>
+        <v>24357</v>
       </c>
       <c r="G23" s="0">
-        <v>3.21</v>
+        <v>1.3700000000000001</v>
       </c>
       <c r="H23" s="0">
-        <v>11.949999999999999</v>
+        <v>11.359999999999999</v>
       </c>
       <c r="I23" s="0">
-        <v>83.530000000000001</v>
+        <v>86.670000000000002</v>
       </c>
       <c r="J23" s="0">
-        <v>1489</v>
+        <v>4101</v>
       </c>
       <c r="K23" s="0">
-        <v>4567.8999999999996</v>
+        <v>11785.01</v>
       </c>
       <c r="L23" s="0">
-        <v>25.579999999999998</v>
+        <v>49.939999999999998</v>
       </c>
       <c r="M23" s="0">
-        <v>0.064000000000000001</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1171,40 +1144,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>25260217147</v>
+        <v>38384100583</v>
       </c>
       <c r="C24" s="0">
-        <v>29815902585</v>
+        <v>46919406680</v>
       </c>
       <c r="D24" s="0">
-        <v>685896</v>
+        <v>1837095</v>
       </c>
       <c r="E24" s="0">
-        <v>185</v>
+        <v>264</v>
       </c>
       <c r="F24" s="0">
-        <v>128824</v>
+        <v>32831</v>
       </c>
       <c r="G24" s="0">
-        <v>2.96</v>
+        <v>1.29</v>
       </c>
       <c r="H24" s="0">
-        <v>9.5299999999999994</v>
+        <v>13.869999999999999</v>
       </c>
       <c r="I24" s="0">
-        <v>84.719999999999999</v>
+        <v>81.810000000000002</v>
       </c>
       <c r="J24" s="0">
-        <v>1269</v>
+        <v>5414</v>
       </c>
       <c r="K24" s="0">
-        <v>6456.8699999999999</v>
+        <v>10471.700000000001</v>
       </c>
       <c r="L24" s="0">
-        <v>35.289999999999999</v>
+        <v>39.649999999999999</v>
       </c>
       <c r="M24" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1212,40 +1185,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>8968582690</v>
+        <v>13507941855</v>
       </c>
       <c r="C25" s="0">
-        <v>10484481345</v>
+        <v>15801941838</v>
       </c>
       <c r="D25" s="0">
-        <v>783594</v>
+        <v>2081942</v>
       </c>
       <c r="E25" s="0">
-        <v>234</v>
+        <v>318</v>
       </c>
       <c r="F25" s="0">
-        <v>31306</v>
+        <v>11097</v>
       </c>
       <c r="G25" s="0">
-        <v>2.3399999999999999</v>
+        <v>1.46</v>
       </c>
       <c r="H25" s="0">
-        <v>8.3399999999999999</v>
+        <v>13.16</v>
       </c>
       <c r="I25" s="0">
-        <v>85.540000000000006</v>
+        <v>85.480000000000004</v>
       </c>
       <c r="J25" s="0">
-        <v>1431</v>
+        <v>4478</v>
       </c>
       <c r="K25" s="0">
-        <v>7143.7200000000003</v>
+        <v>9604.8099999999995</v>
       </c>
       <c r="L25" s="0">
-        <v>30.530000000000001</v>
+        <v>30.199999999999999</v>
       </c>
       <c r="M25" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1253,40 +1226,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>24029953548</v>
+        <v>58819153428</v>
       </c>
       <c r="C26" s="0">
-        <v>28854891286</v>
+        <v>71140436234</v>
       </c>
       <c r="D26" s="0">
-        <v>1050415</v>
+        <v>1617196</v>
       </c>
       <c r="E26" s="0">
-        <v>200</v>
+        <v>296</v>
       </c>
       <c r="F26" s="0">
-        <v>44495</v>
+        <v>61721</v>
       </c>
       <c r="G26" s="0">
-        <v>1.6200000000000001</v>
+        <v>1.3999999999999999</v>
       </c>
       <c r="H26" s="0">
-        <v>11.539999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="I26" s="0">
-        <v>83.280000000000001</v>
+        <v>82.680000000000007</v>
       </c>
       <c r="J26" s="0">
-        <v>3275</v>
+        <v>4028</v>
       </c>
       <c r="K26" s="0">
-        <v>8005.2799999999997</v>
+        <v>11862.030000000001</v>
       </c>
       <c r="L26" s="0">
-        <v>40.409999999999997</v>
+        <v>41.329999999999998</v>
       </c>
       <c r="M26" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.085000000000000006</v>
       </c>
     </row>
     <row r="27">
@@ -1294,40 +1267,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>15131188759</v>
+        <v>25106726688</v>
       </c>
       <c r="C27" s="0">
-        <v>17776006022</v>
+        <v>31026338195</v>
       </c>
       <c r="D27" s="0">
-        <v>1333534</v>
+        <v>2029192</v>
       </c>
       <c r="E27" s="0">
-        <v>234</v>
+        <v>327</v>
       </c>
       <c r="F27" s="0">
-        <v>20743</v>
+        <v>19655</v>
       </c>
       <c r="G27" s="0">
-        <v>1.5600000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="H27" s="0">
-        <v>12.17</v>
+        <v>12.390000000000001</v>
       </c>
       <c r="I27" s="0">
-        <v>85.120000000000005</v>
+        <v>80.920000000000002</v>
       </c>
       <c r="J27" s="0">
-        <v>3670</v>
+        <v>4793</v>
       </c>
       <c r="K27" s="0">
-        <v>8959.0699999999997</v>
+        <v>13689.07</v>
       </c>
       <c r="L27" s="0">
-        <v>38.369999999999997</v>
+        <v>41.600000000000001</v>
       </c>
       <c r="M27" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.084000000000000005</v>
       </c>
     </row>
     <row r="28">
@@ -1335,409 +1308,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>15814930907</v>
+        <v>710722755743</v>
       </c>
       <c r="C28" s="0">
-        <v>19286103769</v>
+        <v>852596667472</v>
       </c>
       <c r="D28" s="0">
-        <v>1513823</v>
+        <v>784798</v>
       </c>
       <c r="E28" s="0">
-        <v>263</v>
+        <v>174</v>
       </c>
       <c r="F28" s="0">
-        <v>21804</v>
+        <v>3361325</v>
       </c>
       <c r="G28" s="0">
-        <v>1.71</v>
+        <v>3.0899999999999999</v>
       </c>
       <c r="H28" s="0">
-        <v>12.369999999999999</v>
+        <v>10.109999999999999</v>
       </c>
       <c r="I28" s="0">
-        <v>82</v>
+        <v>83.359999999999999</v>
       </c>
       <c r="J28" s="0">
-        <v>3401</v>
+        <v>1292</v>
       </c>
       <c r="K28" s="0">
-        <v>8716.1100000000006</v>
+        <v>6710.0200000000004</v>
       </c>
       <c r="L28" s="0">
-        <v>33.469999999999999</v>
+        <v>35.259999999999998</v>
       </c>
       <c r="M28" s="0">
-        <v>0.070999999999999994</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="0">
-        <v>17469108193</v>
-      </c>
-      <c r="C29" s="0">
-        <v>20300270014</v>
-      </c>
-      <c r="D29" s="0">
-        <v>1819021</v>
-      </c>
-      <c r="E29" s="0">
-        <v>282</v>
-      </c>
-      <c r="F29" s="0">
-        <v>17720</v>
-      </c>
-      <c r="G29" s="0">
-        <v>1.5900000000000001</v>
-      </c>
-      <c r="H29" s="0">
-        <v>13.49</v>
-      </c>
-      <c r="I29" s="0">
-        <v>86.049999999999997</v>
-      </c>
-      <c r="J29" s="0">
-        <v>4065</v>
-      </c>
-      <c r="K29" s="0">
-        <v>9146.3400000000001</v>
-      </c>
-      <c r="L29" s="0">
-        <v>32.450000000000003</v>
-      </c>
-      <c r="M29" s="0">
-        <v>0.068000000000000005</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="0">
-        <v>21222815617</v>
-      </c>
-      <c r="C30" s="0">
-        <v>25117527286</v>
-      </c>
-      <c r="D30" s="0">
-        <v>1747914</v>
-      </c>
-      <c r="E30" s="0">
-        <v>281</v>
-      </c>
-      <c r="F30" s="0">
-        <v>20281</v>
-      </c>
-      <c r="G30" s="0">
-        <v>1.4099999999999999</v>
-      </c>
-      <c r="H30" s="0">
-        <v>12.91</v>
-      </c>
-      <c r="I30" s="0">
-        <v>84.489999999999995</v>
-      </c>
-      <c r="J30" s="0">
-        <v>4409</v>
-      </c>
-      <c r="K30" s="0">
-        <v>9415.2399999999998</v>
-      </c>
-      <c r="L30" s="0">
-        <v>33.520000000000003</v>
-      </c>
-      <c r="M30" s="0">
-        <v>0.070000000000000007</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0">
-        <v>22569392688</v>
-      </c>
-      <c r="C31" s="0">
-        <v>27024216560</v>
-      </c>
-      <c r="D31" s="0">
-        <v>2004764</v>
-      </c>
-      <c r="E31" s="0">
-        <v>298</v>
-      </c>
-      <c r="F31" s="0">
-        <v>16120</v>
-      </c>
-      <c r="G31" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="H31" s="0">
-        <v>13.56</v>
-      </c>
-      <c r="I31" s="0">
-        <v>83.519999999999996</v>
-      </c>
-      <c r="J31" s="0">
-        <v>5677</v>
-      </c>
-      <c r="K31" s="0">
-        <v>9834.1200000000008</v>
-      </c>
-      <c r="L31" s="0">
-        <v>33.289999999999999</v>
-      </c>
-      <c r="M31" s="0">
-        <v>0.067000000000000004</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="0">
-        <v>20432577455</v>
-      </c>
-      <c r="C32" s="0">
-        <v>23576275957</v>
-      </c>
-      <c r="D32" s="0">
-        <v>1322281</v>
-      </c>
-      <c r="E32" s="0">
-        <v>236</v>
-      </c>
-      <c r="F32" s="0">
-        <v>24357</v>
-      </c>
-      <c r="G32" s="0">
-        <v>1.3700000000000001</v>
-      </c>
-      <c r="H32" s="0">
-        <v>11.359999999999999</v>
-      </c>
-      <c r="I32" s="0">
-        <v>86.670000000000002</v>
-      </c>
-      <c r="J32" s="0">
-        <v>4101</v>
-      </c>
-      <c r="K32" s="0">
-        <v>11785.01</v>
-      </c>
-      <c r="L32" s="0">
-        <v>49.939999999999998</v>
-      </c>
-      <c r="M32" s="0">
-        <v>0.10100000000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="0">
-        <v>40079698492</v>
-      </c>
-      <c r="C33" s="0">
-        <v>48898013180</v>
-      </c>
-      <c r="D33" s="0">
-        <v>1914566</v>
-      </c>
-      <c r="E33" s="0">
-        <v>267</v>
-      </c>
-      <c r="F33" s="0">
-        <v>34923</v>
-      </c>
-      <c r="G33" s="0">
-        <v>1.3700000000000001</v>
-      </c>
-      <c r="H33" s="0">
-        <v>14.42</v>
-      </c>
-      <c r="I33" s="0">
-        <v>81.969999999999999</v>
-      </c>
-      <c r="J33" s="0">
-        <v>5279</v>
-      </c>
-      <c r="K33" s="0">
-        <v>10076.57</v>
-      </c>
-      <c r="L33" s="0">
-        <v>37.960000000000001</v>
-      </c>
-      <c r="M33" s="0">
-        <v>0.075999999999999998</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="0">
-        <v>13507941855</v>
-      </c>
-      <c r="C34" s="0">
-        <v>15801941838</v>
-      </c>
-      <c r="D34" s="0">
-        <v>1894717</v>
-      </c>
-      <c r="E34" s="0">
-        <v>318</v>
-      </c>
-      <c r="F34" s="0">
-        <v>11097</v>
-      </c>
-      <c r="G34" s="0">
-        <v>1.3300000000000001</v>
-      </c>
-      <c r="H34" s="0">
-        <v>11.970000000000001</v>
-      </c>
-      <c r="I34" s="0">
-        <v>85.480000000000004</v>
-      </c>
-      <c r="J34" s="0">
-        <v>4478</v>
-      </c>
-      <c r="K34" s="0">
-        <v>10787.83</v>
-      </c>
-      <c r="L34" s="0">
-        <v>33.920000000000002</v>
-      </c>
-      <c r="M34" s="0">
-        <v>0.068000000000000005</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="0">
-        <v>58819153428</v>
-      </c>
-      <c r="C35" s="0">
-        <v>71140436234</v>
-      </c>
-      <c r="D35" s="0">
-        <v>1617196</v>
-      </c>
-      <c r="E35" s="0">
-        <v>296</v>
-      </c>
-      <c r="F35" s="0">
-        <v>61721</v>
-      </c>
-      <c r="G35" s="0">
-        <v>1.3999999999999999</v>
-      </c>
-      <c r="H35" s="0">
-        <v>11.6</v>
-      </c>
-      <c r="I35" s="0">
-        <v>82.680000000000007</v>
-      </c>
-      <c r="J35" s="0">
-        <v>4028</v>
-      </c>
-      <c r="K35" s="0">
-        <v>11862.030000000001</v>
-      </c>
-      <c r="L35" s="0">
-        <v>41.329999999999998</v>
-      </c>
-      <c r="M35" s="0">
-        <v>0.085000000000000006</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="0">
-        <v>25106726688</v>
-      </c>
-      <c r="C36" s="0">
-        <v>31026338195</v>
-      </c>
-      <c r="D36" s="0">
-        <v>2029192</v>
-      </c>
-      <c r="E36" s="0">
-        <v>327</v>
-      </c>
-      <c r="F36" s="0">
-        <v>19655</v>
-      </c>
-      <c r="G36" s="0">
-        <v>1.29</v>
-      </c>
-      <c r="H36" s="0">
-        <v>12.390000000000001</v>
-      </c>
-      <c r="I36" s="0">
-        <v>80.920000000000002</v>
-      </c>
-      <c r="J36" s="0">
-        <v>4793</v>
-      </c>
-      <c r="K36" s="0">
-        <v>13689.07</v>
-      </c>
-      <c r="L36" s="0">
-        <v>41.600000000000001</v>
-      </c>
-      <c r="M36" s="0">
-        <v>0.084000000000000005</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="0">
-        <v>1133669858258</v>
-      </c>
-      <c r="C37" s="0">
-        <v>1383207042733</v>
-      </c>
-      <c r="D37" s="0">
-        <v>543572</v>
-      </c>
-      <c r="E37" s="0">
-        <v>141</v>
-      </c>
-      <c r="F37" s="0">
-        <v>8644551</v>
-      </c>
-      <c r="G37" s="0">
-        <v>3.3999999999999999</v>
-      </c>
-      <c r="H37" s="0">
-        <v>8.7799999999999994</v>
-      </c>
-      <c r="I37" s="0">
-        <v>81.959999999999994</v>
-      </c>
-      <c r="J37" s="0">
-        <v>938</v>
-      </c>
-      <c r="K37" s="0">
-        <v>5234.79</v>
-      </c>
-      <c r="L37" s="0">
-        <v>32.560000000000002</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.085000000000000006</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
   </sheetData>
